--- a/doc/教师名单.xlsx
+++ b/doc/教师名单.xlsx
@@ -1,26 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10811"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wuwoo/Desktop/work/_育英星宠/YuYingPets/doc/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D20A3DE-711B-D34B-A694-1CAB7DBD731A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$101</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="251">
   <si>
     <t>姓名</t>
   </si>
@@ -34,680 +44,763 @@
     <t>任课班级</t>
   </si>
   <si>
+    <t>索懿</t>
+  </si>
+  <si>
+    <t>15187209824</t>
+  </si>
+  <si>
+    <t>校长,学校管理员</t>
+  </si>
+  <si>
     <t>徐晓旭</t>
   </si>
   <si>
+    <t>13988585939</t>
+  </si>
+  <si>
+    <t>副校长,年级主任</t>
+  </si>
+  <si>
+    <t>八年级 58班（英语）</t>
+  </si>
+  <si>
     <t>高锦霞</t>
   </si>
   <si>
+    <t>学科组长</t>
+  </si>
+  <si>
+    <t>九年级 40班（信息技术）,九年级 41班（信息技术）,九年级 42班（信息技术）,九年级 43班（信息技术）,九年级 44班（信息技术）,九年级 45班（信息技术）,九年级 46班（信息技术）,九年级 47班（信息技术）,九年级 48班（信息技术）,九年级 49班（信息技术）,八年级 50班（信息技术）,八年级 51班（信息技术）,八年级 52班（信息技术）,八年级 53班（信息技术）,八年级 54班（信息技术）,七年级 67班（信息技术）,七年级 68班（信息技术）,七年级 69班（信息技术）,七年级 70班（信息技术）,七年级 71班（信息技术）,七年级 72班（信息技术）</t>
+  </si>
+  <si>
     <t>薛薇</t>
   </si>
   <si>
+    <t>班主任(40班）</t>
+  </si>
+  <si>
+    <t>九年级 40班（语文）,九年级 41班（语文）</t>
+  </si>
+  <si>
     <t>仇梦圆</t>
   </si>
   <si>
+    <t>备课组长,学科组长</t>
+  </si>
+  <si>
+    <t>九年级 40班（生物）,九年级 41班（生物）,九年级 42班（生物）,九年级 43班（生物）,九年级 44班（生物）,九年级 45班（化学）,九年级 46班（化学）,九年级 47班（化学）</t>
+  </si>
+  <si>
     <t>马丽</t>
   </si>
   <si>
+    <t>备课组长,校长,学科组长,考试管理员</t>
+  </si>
+  <si>
+    <t>八年级 50班（英语）,八年级 51班（英语）</t>
+  </si>
+  <si>
     <t>段秋实</t>
   </si>
   <si>
+    <t>九年级德育干事</t>
+  </si>
+  <si>
+    <t>九年级 42班（数学）,九年级 43班（数学）</t>
+  </si>
+  <si>
     <t>杨云萍</t>
   </si>
   <si>
+    <t>备课组长,班主任（46班）,学科组长</t>
+  </si>
+  <si>
+    <t>九年级 44班（政治,道德与法治）,九年级 45班（政治,道德与法治）,九年级 46班（政治,道德与法治）,九年级 47班（政治,道德与法治）,九年级 48班（政治,道德与法治）,九年级 49班（政治,道德与法治）</t>
+  </si>
+  <si>
     <t>张筱颖</t>
   </si>
   <si>
+    <t>班主任（69班）</t>
+  </si>
+  <si>
+    <t>七年级 69班（语文）,七年级 70班（语文）</t>
+  </si>
+  <si>
     <t>马思雨</t>
   </si>
   <si>
+    <t>备课组长</t>
+  </si>
+  <si>
+    <t>八年级 56班（语文）,八年级 57班（语文）</t>
+  </si>
+  <si>
     <t>李俊峰</t>
   </si>
   <si>
+    <t>年级主任,班主任（66班）</t>
+  </si>
+  <si>
+    <t>七年级 65班（生物）,七年级 66班（生物）,七年级 71班（生物）,七年级 72班（生物）</t>
+  </si>
+  <si>
     <t>王昱丹</t>
   </si>
   <si>
+    <t>九年级 40班（历史）,九年级 41班（历史）,九年级 42班（历史）,九年级 43班（历史）,九年级 44班（历史）,九年级 45班（历史）,九年级 46班（历史）</t>
+  </si>
+  <si>
     <t>徐娜</t>
   </si>
   <si>
+    <t>学科组长，八年级德育干事</t>
+  </si>
+  <si>
+    <t>九年级 45班（生物）,九年级 46班（生物）,九年级 47班（生物）,九年级 48班（生物）,九年级 49班（生物）,八年级 51班（生物）,八年级 52班（生物）,八年级 53班（生物）,八年级 55班（生物）,八年级 60班（生物）</t>
+  </si>
+  <si>
     <t>李生贵</t>
   </si>
   <si>
+    <t>九年级 43班（体育）,九年级 44班（体育）,九年级 45班（体育）,九年级 46班（体育）,七年级 65班（体育）,七年级 66班（体育）,七年级 67班（体育）</t>
+  </si>
+  <si>
     <t>陶翀</t>
   </si>
   <si>
+    <t>学科组长，七年级德育干事</t>
+  </si>
+  <si>
+    <t>九年级 40班（美术）,九年级 41班（美术）,九年级 42班（美术）,九年级 43班（美术）,九年级 44班（美术）,七年级 61班（美术）,七年级 62班（美术）,七年级 63班（美术）,七年级 64班（美术）,七年级 65班（美术）,七年级 66班（美术）,七年级 67班（美术）,七年级 68班（美术）,七年级 69班（美术）,七年级 70班（美术）,七年级 71班（美术）,七年级 72班（美术）</t>
+  </si>
+  <si>
     <t>徐梦丝</t>
   </si>
   <si>
+    <t>考试管理员（教务干事）</t>
+  </si>
+  <si>
+    <t>八年级 55班（信息技术）,八年级 56班（信息技术）,八年级 57班（信息技术）,八年级 58班（信息技术）,八年级 59班（信息技术）,八年级 60班（信息技术）,七年级 61班（信息技术）,七年级 62班（信息技术）,七年级 63班（信息技术）,七年级 64班（信息技术）,七年级 65班（信息技术）,七年级 66班（信息技术）</t>
+  </si>
+  <si>
+    <t>冯云炜</t>
+  </si>
+  <si>
+    <t>18487130341</t>
+  </si>
+  <si>
     <t>张杜柔</t>
   </si>
   <si>
+    <t>班主任（65班）</t>
+  </si>
+  <si>
+    <t>七年级 65班（数学）,七年级 66班（数学）</t>
+  </si>
+  <si>
     <t>陆晓琼</t>
   </si>
   <si>
+    <t>班主任（70班）</t>
+  </si>
+  <si>
+    <t>七年级 69班（英语）,七年级 70班（英语）</t>
+  </si>
+  <si>
     <t>钟佩男</t>
   </si>
   <si>
+    <t>九年级 49班（化学）</t>
+  </si>
+  <si>
     <t>杨海燕</t>
   </si>
   <si>
+    <t>九年级 41班（物理）,九年级 43班（物理）,九年级 47班（物理）</t>
+  </si>
+  <si>
     <t>刘天微</t>
   </si>
   <si>
+    <t>年级主任,班主任（45班）</t>
+  </si>
+  <si>
+    <t>九年级 45班（英语）,九年级 46班（英语）</t>
+  </si>
+  <si>
     <t>张美佳</t>
   </si>
   <si>
+    <t>班主任,学科组长</t>
+  </si>
+  <si>
+    <t>九年级 47班（地理）,九年级 48班（地理）,九年级 49班（地理）,八年级 50班（地理）,八年级 51班（地理）,八年级 54班（地理）,八年级 55班（地理）,八年级 56班（地理）,八年级 57班（地理）</t>
+  </si>
+  <si>
     <t>吴锦晖</t>
   </si>
   <si>
+    <t>九年级 42班（语文）,九年级 47班（语文）</t>
+  </si>
+  <si>
     <t>李雪梅</t>
   </si>
   <si>
+    <t>备课组长,班主任（40班）,学科组长</t>
+  </si>
+  <si>
+    <t>九年级 40班（数学）,九年级 41班（数学）</t>
+  </si>
+  <si>
     <t>张玲</t>
   </si>
   <si>
+    <t>九年级 40班（化学）,九年级 41班（化学）,九年级 43班（化学）</t>
+  </si>
+  <si>
     <t>赵晓慧</t>
   </si>
   <si>
+    <t>八年级 53班（物理）,八年级 59班（物理）,八年级 60班（物理）,七年级 67班（物理）,七年级 68班（物理）,七年级 69班（物理）</t>
+  </si>
+  <si>
     <t>石玉锦</t>
   </si>
   <si>
+    <t>备课组长,班主任（63班）</t>
+  </si>
+  <si>
+    <t>七年级 63班（数学）,七年级 64班（数学）</t>
+  </si>
+  <si>
     <t>李丹妮</t>
   </si>
   <si>
+    <t>八年级 58班（历史）,八年级 59班（历史）,八年级 60班（历史）,八年级 57班（历史）,八年级 56班（历史）</t>
+  </si>
+  <si>
     <t>杨金灿</t>
   </si>
   <si>
+    <t>八年级 57班（体育）,八年级 58班（体育）,八年级 59班（体育）,八年级 60班（体育）,九年级 40班（体育）,九年级 41班（体育）,九年级 42班（体育）</t>
+  </si>
+  <si>
     <t>张慧梅</t>
   </si>
   <si>
+    <t>班主任（71班）</t>
+  </si>
+  <si>
+    <t>九年级 40班（政治,道德与法治）,九年级 41班（政治,道德与法治）,九年级 42班（政治,道德与法治）,九年级 43班（政治,道德与法治）,七年级 71班（政治,道德与法治）,七年级 72班（政治,道德与法治）</t>
+  </si>
+  <si>
     <t>邵成会</t>
   </si>
   <si>
+    <t>备课组长,班主任（68班）</t>
+  </si>
+  <si>
+    <t>七年级 67班（语文）,七年级 68班（语文）</t>
+  </si>
+  <si>
     <t>张忍</t>
   </si>
   <si>
+    <t>九年级 44班（物理）,九年级 45班（物理）,九年级 46班（物理）</t>
+  </si>
+  <si>
     <t>张婷婷</t>
   </si>
   <si>
+    <t>八年级 50班（生物）,八年级 54班（生物）,七年级 63班（生物）,七年级 64班（生物）</t>
+  </si>
+  <si>
     <t>杨玥</t>
   </si>
   <si>
+    <t>班主任（49班）</t>
+  </si>
+  <si>
+    <t>九年级 48班（语文）,九年级 49班（语文）</t>
+  </si>
+  <si>
     <t>许杰</t>
   </si>
   <si>
     <t>薛洁</t>
   </si>
   <si>
+    <t>八年级 58班（数学）,八年级 59班（数学）</t>
+  </si>
+  <si>
     <t>李薇</t>
   </si>
   <si>
+    <t>八年级 50班（数学）,八年级 51班（数学）</t>
+  </si>
+  <si>
     <t>和凤琴</t>
   </si>
   <si>
+    <t>八年级 50班（政治,道德与法治）,八年级 51班（政治,道德与法治）,八年级 52班（政治,道德与法治）,七年级 69班（政治）,七年级 70班（政治）,七年级 64班（道德与法治）,七年级 65班（道德与法治）,七年级 66班（道德与法治）,七年级 67班（道德与法治）</t>
+  </si>
+  <si>
     <t>黄周云</t>
   </si>
   <si>
+    <t>备课组长,班主任（56班）</t>
+  </si>
+  <si>
+    <t>八年级 56班（政治,道德与法治）,八年级 57班（政治,道德与法治）,八年级 58班（政治,道德与法治）,八年级 59班（政治,道德与法治）,八年级 60班（政治,道德与法治）,八年级 55班（道德与法治）</t>
+  </si>
+  <si>
     <t>马千子</t>
   </si>
   <si>
+    <t>备课组长,班主任（54班）</t>
+  </si>
+  <si>
+    <t>八年级 54班（数学）,八年级 55班（数学）</t>
+  </si>
+  <si>
     <t>赵萍</t>
   </si>
   <si>
+    <t>备课组长,年级主任,班主任（58班）</t>
+  </si>
+  <si>
+    <t>八年级 56班（生物）,八年级 57班（生物）,八年级 58班（生物）,八年级 59班（生物）,八年级 50班（数学,英语,物理）</t>
+  </si>
+  <si>
     <t>阿灿琴</t>
   </si>
   <si>
+    <t>备课组长,班主任（50班）</t>
+  </si>
+  <si>
+    <t>八年级 50班（历史）,八年级 51班（历史）,八年级 52班（历史）,八年级 53班（历史）,八年级 54班（历史）,八年级 55班（历史）</t>
+  </si>
+  <si>
     <t>杨娇</t>
   </si>
   <si>
+    <t>班主任（44班）</t>
+  </si>
+  <si>
+    <t>九年级 42班（英语）,九年级 43班（英语）</t>
+  </si>
+  <si>
     <t>张敏芝</t>
   </si>
   <si>
+    <t>班主任（57班）</t>
+  </si>
+  <si>
+    <t>八年级 56班（英语）,八年级 57班（英语）</t>
+  </si>
+  <si>
     <t>李春梅</t>
   </si>
   <si>
+    <t>九年级 40班（物理）,八年级 56班（物理）,八年级 57班（物理）</t>
+  </si>
+  <si>
     <t>袁梅</t>
   </si>
   <si>
+    <t>班主任（60班）</t>
+  </si>
+  <si>
+    <t>八年级 59班（语文）,八年级 60班（语文）</t>
+  </si>
+  <si>
     <t>左家美</t>
   </si>
   <si>
+    <t>九年级 45班（语文）,九年级 46班（语文）</t>
+  </si>
+  <si>
     <t>赵莎莎</t>
   </si>
   <si>
+    <t>德育干事</t>
+  </si>
+  <si>
+    <t>九年级 45班（美术）,九年级 46班（美术）,九年级 47班（美术）,九年级 48班（美术）,九年级 49班（美术）,八年级 55班（美术）,八年级 56班（美术）,八年级 57班（美术）,八年级 58班（美术）,八年级 59班（美术）,八年级 60班（美术）,八年级 54班（美术）,八年级 53班（美术）,八年级 52班（美术）,八年级 51班（美术）,八年级 50班（美术）</t>
+  </si>
+  <si>
     <t>施倩</t>
   </si>
   <si>
+    <t>九年级 45班（音乐）,九年级 46班（音乐）,八年级 50班（音乐）,八年级 51班（音乐）,八年级 52班（音乐）,八年级 53班（音乐）,八年级 54班（音乐）,八年级 55班（音乐）,八年级 56班（音乐）,八年级 57班（音乐）,八年级 58班（音乐）,八年级 59班（音乐）,八年级 60班（音乐）,九年级 47班（音乐）,九年级 48班（音乐）,九年级 49班（音乐）</t>
+  </si>
+  <si>
     <t>李姝雯</t>
   </si>
   <si>
+    <t>班主任（62班）</t>
+  </si>
+  <si>
+    <t>七年级 61班（语文）,七年级 62班（语文）</t>
+  </si>
+  <si>
     <t>王鑫池</t>
   </si>
   <si>
+    <t>班主任（55班）</t>
+  </si>
+  <si>
+    <t>八年级 54班（英语）,八年级 55班（英语）</t>
+  </si>
+  <si>
     <t>关森</t>
   </si>
   <si>
+    <t>九年级 40班（音乐）,九年级 41班（音乐）,九年级 42班（音乐）,九年级 43班（音乐）,九年级 44班（音乐）,七年级 61班（音乐）,七年级 62班（音乐）,七年级 63班（音乐）,七年级 64班（音乐）,七年级 65班（音乐）,七年级 66班（音乐）,七年级 67班（音乐）,七年级 68班（音乐）,七年级 69班（音乐）,七年级 70班（音乐）,七年级 71班（音乐）,七年级 72班（音乐）</t>
+  </si>
+  <si>
     <t>孙加慧</t>
   </si>
   <si>
+    <t>七年级 71班（英语）,七年级 72班（英语）</t>
+  </si>
+  <si>
     <t>徐韬</t>
   </si>
   <si>
+    <t>七年级 71班（语文）,七年级 72班（语文）</t>
+  </si>
+  <si>
+    <t>李扬</t>
+  </si>
+  <si>
+    <t>15317636702</t>
+  </si>
+  <si>
+    <t>八年级 54班（物理）,八年级 55班（物理）,八年级 58班（物理）,七年级 70班（物理）,七年级 71班（物理）,七年级 72班（物理）</t>
+  </si>
+  <si>
     <t>向先涛</t>
   </si>
   <si>
+    <t>备课组长,班主任（72班），七年级教务干事</t>
+  </si>
+  <si>
+    <t>九年级 40班（地理）,九年级 41班（地理）,九年级 42班（地理）,九年级 43班（地理）,九年级 44班（地理）,七年级 67班（地理）,七年级 68班（地理）,七年级 69班（地理）,七年级 70班（地理）,七年级 71班（地理）,七年级 72班（地理）</t>
+  </si>
+  <si>
     <t>兰秀杰</t>
   </si>
   <si>
+    <t>备课组长,班主任（43班）,学科组长</t>
+  </si>
+  <si>
+    <t>九年级 43班（语文）,九年级 44班（语文）</t>
+  </si>
+  <si>
     <t>夏聂</t>
   </si>
   <si>
+    <t>班主任（48班）</t>
+  </si>
+  <si>
+    <t>九年级 48班（数学）,九年级 49班（数学）</t>
+  </si>
+  <si>
     <t>赵庆兴</t>
   </si>
   <si>
+    <t>九年级 46班（数学）,九年级 47班（数学）</t>
+  </si>
+  <si>
     <t>翟瑶</t>
   </si>
   <si>
+    <t>班主任（47班）</t>
+  </si>
+  <si>
+    <t>九年级 47班（英语）,九年级 48班（英语）</t>
+  </si>
+  <si>
     <t>王清海</t>
   </si>
   <si>
+    <t>七年级 61班（历史）,七年级 62班（历史）,七年级 63班（历史）,七年级 64班（历史）</t>
+  </si>
+  <si>
     <t>胡赵兰</t>
   </si>
   <si>
+    <t>备课组长,班主任（44班）,学科组长</t>
+  </si>
+  <si>
+    <t>九年级 44班（英语）,九年级 49班（英语）</t>
+  </si>
+  <si>
     <t>黄应珍</t>
   </si>
   <si>
+    <t>九年级 40班（英语）,九年级 41班（英语）</t>
+  </si>
+  <si>
     <t>刘云镜</t>
   </si>
   <si>
+    <t>八年级 53班（数学）</t>
+  </si>
+  <si>
     <t>周晓静</t>
   </si>
   <si>
+    <t>七年级 71班（数学）,七年级 72班（数学）</t>
+  </si>
+  <si>
     <t>姚玉露</t>
   </si>
   <si>
+    <t>班主任（52班）</t>
+  </si>
+  <si>
+    <t>八年级 52班（语文）,八年级 53班（语文）</t>
+  </si>
+  <si>
     <t>黄霞</t>
   </si>
   <si>
+    <t>班主任（53班）</t>
+  </si>
+  <si>
+    <t>八年级 52班（英语）,八年级 53班（英语）</t>
+  </si>
+  <si>
     <t>张敏</t>
   </si>
   <si>
+    <t>班主任（59班）</t>
+  </si>
+  <si>
+    <t>八年级 59班（英语）,八年级 60班（英语）</t>
+  </si>
+  <si>
     <t>雷永存</t>
   </si>
   <si>
+    <t>七年级 63班（英语）,七年级 64班（英语）</t>
+  </si>
+  <si>
     <t>杨葵</t>
   </si>
   <si>
+    <t>八年级教务干事</t>
+  </si>
+  <si>
+    <t>八年级 54班（语文）,八年级 55班（语文）</t>
+  </si>
+  <si>
     <t>庄明珠</t>
   </si>
   <si>
+    <t>八年级 50班（语文）,八年级 51班（语文）</t>
+  </si>
+  <si>
     <t>杨娜</t>
   </si>
   <si>
+    <t>八年级 58班（语文）</t>
+  </si>
+  <si>
     <t>张娜</t>
   </si>
   <si>
+    <t>八年级 56班（数学）,八年级 57班（数学）</t>
+  </si>
+  <si>
     <t>涂龙</t>
   </si>
   <si>
+    <t>八年级 54班（体育）,八年级 55班（体育）,八年级 56班（体育）,七年级 61班（体育）,七年级 62班（体育）,七年级 63班（体育）,七年级 64班（体育）</t>
+  </si>
+  <si>
     <t>张啟萌</t>
   </si>
   <si>
+    <t>九年级 48班（物理）,九年级 49班（物理）,九年级 42班（物理）</t>
+  </si>
+  <si>
     <t>杨美靖</t>
   </si>
   <si>
+    <t>九年级教务干事</t>
+  </si>
+  <si>
+    <t>九年级 42班（化学）,九年级 44班（化学）,九年级 48班（化学）</t>
+  </si>
+  <si>
     <t>蔡东方</t>
   </si>
   <si>
+    <t>八年级 52班（地理）,八年级 59班（地理）,八年级 60班（地理）,九年级 45班（地理）,九年级 46班（地理）,八年级 53班（地理）,八年级 58班（地理）</t>
+  </si>
+  <si>
     <t>黄珠莹</t>
   </si>
   <si>
-    <t>索懿</t>
+    <t>七年级 61班（生物）,七年级 62班（生物）,七年级 67班（生物）,七年级 68班（生物）,七年级 69班（生物）,七年级 70班（生物）</t>
   </si>
   <si>
     <t>王重坤</t>
   </si>
   <si>
+    <t>八年级 60班（数学）,八年级 52班（数学）</t>
+  </si>
+  <si>
     <t>谢星平</t>
   </si>
   <si>
+    <t>七年级 65班（英语）,七年级 66班（英语）</t>
+  </si>
+  <si>
     <t>曹凤亮</t>
   </si>
   <si>
+    <t>七年级 67班（数学）,七年级 68班（数学）</t>
+  </si>
+  <si>
     <t>王青梅</t>
   </si>
   <si>
+    <t>八年级 53班（政治,道德与法治）,八年级 54班（政治,道德与法治）,八年级 55班（政治）,七年级 67班（政治）,七年级 68班（政治,道德与法治）,七年级 69班（道德与法治）,七年级 70班（道德与法治）</t>
+  </si>
+  <si>
     <t>周京峰</t>
   </si>
   <si>
+    <t>七年级 65班（历史）,七年级 66班（历史）,七年级 67班（历史）,七年级 68班（历史）,七年级 69班（历史）</t>
+  </si>
+  <si>
     <t>张飞飞</t>
   </si>
   <si>
+    <t>七年级 61班（地理）,七年级 62班（地理）,七年级 63班（地理）,七年级 64班（地理）,七年级 65班（地理）,七年级 66班（地理）</t>
+  </si>
+  <si>
     <t>张亚怡</t>
   </si>
   <si>
+    <t>班主任（67班）</t>
+  </si>
+  <si>
+    <t>七年级 67班（英语）,七年级 68班（英语）</t>
+  </si>
+  <si>
     <t>薛倩</t>
   </si>
   <si>
+    <t>九年级 47班（历史）,九年级 48班（历史）,九年级 49班（历史）,七年级 70班（历史）,七年级 71班（历史）,七年级 72班（历史）</t>
+  </si>
+  <si>
     <t>王瑞姬</t>
   </si>
   <si>
+    <t>七年级 69班（数学）,七年级 70班（数学）</t>
+  </si>
+  <si>
     <t>杨润芝</t>
   </si>
   <si>
+    <t>九年级 44班（数学）,九年级 45班（数学）</t>
+  </si>
+  <si>
     <t>张甜</t>
   </si>
   <si>
+    <t>班主任（64班）</t>
+  </si>
+  <si>
+    <t>七年级 63班（语文）,七年级 64班（语文）</t>
+  </si>
+  <si>
     <t>王雪梅</t>
   </si>
   <si>
+    <t>七年级 66班（语文）,七年级 65班（语文）</t>
+  </si>
+  <si>
     <t>王鑫全</t>
   </si>
   <si>
+    <t>八年级 50班（体育）,八年级 51班（体育）,八年级 52班（体育）,八年级 53班（体育）,七年级 68班（体育）,七年级 69班（体育）</t>
+  </si>
+  <si>
     <t>段世杰</t>
   </si>
   <si>
+    <t>八年级 51班（物理）,八年级 52班（物理）,八年级 50班（物理）,七年级 61班（物理）,七年级 62班（物理）,七年级 63班（物理）,七年级 64班（物理）,七年级 65班（物理）,七年级 66班（物理）</t>
+  </si>
+  <si>
     <t>王德海</t>
   </si>
   <si>
+    <t>班主任（61班）</t>
+  </si>
+  <si>
+    <t>七年级 61班（数学）,七年级 62班（数学）</t>
+  </si>
+  <si>
     <t>唐兴龙</t>
   </si>
   <si>
+    <t>九年级 47班（体育）,九年级 48班（体育）,九年级 49班（体育）,七年级 70班（体育）,七年级 71班（体育）,七年级 72班（体育）</t>
+  </si>
+  <si>
     <t>云正杨</t>
   </si>
   <si>
-    <t>校长,学校管理员</t>
-  </si>
-  <si>
-    <t>副校长,年级主任</t>
-  </si>
-  <si>
-    <t>学科组长</t>
-  </si>
-  <si>
-    <t>班主任</t>
-  </si>
-  <si>
-    <t>备课组长,学科组长</t>
-  </si>
-  <si>
-    <t>备课组长,校长,学科组长,考试管理员</t>
-  </si>
-  <si>
-    <t>备课组长,班主任,学科组长</t>
-  </si>
-  <si>
-    <t>备课组长</t>
-  </si>
-  <si>
-    <t>年级主任,班主任</t>
-  </si>
-  <si>
-    <t>考试管理员</t>
-  </si>
-  <si>
-    <t>班主任,学科组长</t>
-  </si>
-  <si>
-    <t>备课组长,班主任</t>
-  </si>
-  <si>
-    <t>备课组长,年级主任,班主任</t>
-  </si>
-  <si>
-    <t>八年级 58班（英语）</t>
-  </si>
-  <si>
-    <t>九年级 40班（信息技术）,九年级 41班（信息技术）,九年级 42班（信息技术）,九年级 43班（信息技术）,九年级 44班（信息技术）,九年级 45班（信息技术）,九年级 46班（信息技术）,九年级 47班（信息技术）,九年级 48班（信息技术）,九年级 49班（信息技术）,八年级 50班（信息技术）,八年级 51班（信息技术）,八年级 52班（信息技术）,八年级 53班（信息技术）,八年级 54班（信息技术）,七年级 67班（信息技术）,七年级 68班（信息技术）,七年级 69班（信息技术）,七年级 70班（信息技术）,七年级 71班（信息技术）,七年级 72班（信息技术）</t>
-  </si>
-  <si>
-    <t>九年级 40班（语文）,九年级 41班（语文）</t>
-  </si>
-  <si>
-    <t>九年级 40班（生物）,九年级 41班（生物）,九年级 42班（生物）,九年级 43班（生物）,九年级 44班（生物）,九年级 45班（化学）,九年级 46班（化学）,九年级 47班（化学）</t>
-  </si>
-  <si>
-    <t>八年级 50班（英语）,八年级 51班（英语）</t>
-  </si>
-  <si>
-    <t>九年级 42班（数学）,九年级 43班（数学）</t>
-  </si>
-  <si>
-    <t>九年级 44班（政治,道德与法治）,九年级 45班（政治,道德与法治）,九年级 46班（政治,道德与法治）,九年级 47班（政治,道德与法治）,九年级 48班（政治,道德与法治）,九年级 49班（政治,道德与法治）</t>
-  </si>
-  <si>
-    <t>七年级 69班（语文）,七年级 70班（语文）</t>
-  </si>
-  <si>
-    <t>八年级 56班（语文）,八年级 57班（语文）</t>
-  </si>
-  <si>
-    <t>七年级 65班（生物）,七年级 66班（生物）,七年级 71班（生物）,七年级 72班（生物）</t>
-  </si>
-  <si>
-    <t>九年级 40班（历史）,九年级 41班（历史）,九年级 42班（历史）,九年级 43班（历史）,九年级 44班（历史）,九年级 45班（历史）,九年级 46班（历史）</t>
-  </si>
-  <si>
-    <t>九年级 45班（生物）,九年级 46班（生物）,九年级 47班（生物）,九年级 48班（生物）,九年级 49班（生物）,八年级 51班（生物）,八年级 52班（生物）,八年级 53班（生物）,八年级 55班（生物）,八年级 60班（生物）</t>
-  </si>
-  <si>
-    <t>九年级 43班（体育）,九年级 44班（体育）,九年级 45班（体育）,九年级 46班（体育）,七年级 65班（体育）,七年级 66班（体育）,七年级 67班（体育）</t>
-  </si>
-  <si>
-    <t>九年级 40班（美术）,九年级 41班（美术）,九年级 42班（美术）,九年级 43班（美术）,九年级 44班（美术）,七年级 61班（美术）,七年级 62班（美术）,七年级 63班（美术）,七年级 64班（美术）,七年级 65班（美术）,七年级 66班（美术）,七年级 67班（美术）,七年级 68班（美术）,七年级 69班（美术）,七年级 70班（美术）,七年级 71班（美术）,七年级 72班（美术）</t>
-  </si>
-  <si>
-    <t>八年级 55班（信息技术）,八年级 56班（信息技术）,八年级 57班（信息技术）,八年级 58班（信息技术）,八年级 59班（信息技术）,八年级 60班（信息技术）,七年级 61班（信息技术）,七年级 62班（信息技术）,七年级 63班（信息技术）,七年级 64班（信息技术）,七年级 65班（信息技术）,七年级 66班（信息技术）</t>
-  </si>
-  <si>
-    <t>七年级 65班（数学）,七年级 66班（数学）</t>
-  </si>
-  <si>
-    <t>七年级 69班（英语）,七年级 70班（英语）</t>
-  </si>
-  <si>
-    <t>九年级 49班（化学）</t>
-  </si>
-  <si>
-    <t>九年级 41班（物理）,九年级 43班（物理）,九年级 47班（物理）</t>
-  </si>
-  <si>
-    <t>九年级 45班（英语）,九年级 46班（英语）</t>
-  </si>
-  <si>
-    <t>九年级 47班（地理）,九年级 48班（地理）,九年级 49班（地理）,八年级 50班（地理）,八年级 51班（地理）,八年级 54班（地理）,八年级 55班（地理）,八年级 56班（地理）,八年级 57班（地理）</t>
-  </si>
-  <si>
-    <t>九年级 42班（语文）,九年级 47班（语文）</t>
-  </si>
-  <si>
-    <t>九年级 40班（数学）,九年级 41班（数学）</t>
-  </si>
-  <si>
-    <t>九年级 40班（化学）,九年级 41班（化学）,九年级 43班（化学）</t>
-  </si>
-  <si>
-    <t>八年级 53班（物理）,八年级 59班（物理）,八年级 60班（物理）,七年级 67班（物理）,七年级 68班（物理）,七年级 69班（物理）</t>
-  </si>
-  <si>
-    <t>七年级 63班（数学）,七年级 64班（数学）</t>
-  </si>
-  <si>
-    <t>八年级 58班（历史）,八年级 59班（历史）,八年级 60班（历史）,八年级 57班（历史）,八年级 56班（历史）</t>
-  </si>
-  <si>
-    <t>八年级 57班（体育）,八年级 58班（体育）,八年级 59班（体育）,八年级 60班（体育）,九年级 40班（体育）,九年级 41班（体育）,九年级 42班（体育）</t>
-  </si>
-  <si>
-    <t>九年级 40班（政治,道德与法治）,九年级 41班（政治,道德与法治）,九年级 42班（政治,道德与法治）,九年级 43班（政治,道德与法治）,七年级 71班（政治,道德与法治）,七年级 72班（政治,道德与法治）</t>
-  </si>
-  <si>
-    <t>七年级 67班（语文）,七年级 68班（语文）</t>
-  </si>
-  <si>
-    <t>九年级 44班（物理）,九年级 45班（物理）,九年级 46班（物理）</t>
-  </si>
-  <si>
-    <t>八年级 50班（生物）,八年级 54班（生物）,七年级 63班（生物）,七年级 64班（生物）</t>
-  </si>
-  <si>
-    <t>九年级 48班（语文）,九年级 49班（语文）</t>
-  </si>
-  <si>
-    <t>八年级 58班（数学）,八年级 59班（数学）</t>
-  </si>
-  <si>
-    <t>八年级 50班（数学）,八年级 51班（数学）</t>
-  </si>
-  <si>
-    <t>八年级 50班（政治,道德与法治）,八年级 51班（政治,道德与法治）,八年级 52班（政治,道德与法治）,七年级 69班（政治）,七年级 70班（政治）,七年级 64班（道德与法治）,七年级 65班（道德与法治）,七年级 66班（道德与法治）,七年级 67班（道德与法治）</t>
-  </si>
-  <si>
-    <t>八年级 56班（政治,道德与法治）,八年级 57班（政治,道德与法治）,八年级 58班（政治,道德与法治）,八年级 59班（政治,道德与法治）,八年级 60班（政治,道德与法治）,八年级 55班（道德与法治）</t>
-  </si>
-  <si>
-    <t>八年级 54班（数学）,八年级 55班（数学）</t>
-  </si>
-  <si>
-    <t>八年级 56班（生物）,八年级 57班（生物）,八年级 58班（生物）,八年级 59班（生物）,八年级 50班（数学,英语,物理）</t>
-  </si>
-  <si>
-    <t>八年级 50班（历史）,八年级 51班（历史）,八年级 52班（历史）,八年级 53班（历史）,八年级 54班（历史）,八年级 55班（历史）</t>
-  </si>
-  <si>
-    <t>九年级 42班（英语）,九年级 43班（英语）</t>
-  </si>
-  <si>
-    <t>八年级 56班（英语）,八年级 57班（英语）</t>
-  </si>
-  <si>
-    <t>九年级 40班（物理）,八年级 56班（物理）,八年级 57班（物理）</t>
-  </si>
-  <si>
-    <t>八年级 59班（语文）,八年级 60班（语文）</t>
-  </si>
-  <si>
-    <t>九年级 45班（语文）,九年级 46班（语文）</t>
-  </si>
-  <si>
-    <t>九年级 45班（美术）,九年级 46班（美术）,九年级 47班（美术）,九年级 48班（美术）,九年级 49班（美术）,八年级 55班（美术）,八年级 56班（美术）,八年级 57班（美术）,八年级 58班（美术）,八年级 59班（美术）,八年级 60班（美术）,八年级 54班（美术）,八年级 53班（美术）,八年级 52班（美术）,八年级 51班（美术）,八年级 50班（美术）</t>
-  </si>
-  <si>
-    <t>九年级 45班（音乐）,九年级 46班（音乐）,八年级 50班（音乐）,八年级 51班（音乐）,八年级 52班（音乐）,八年级 53班（音乐）,八年级 54班（音乐）,八年级 55班（音乐）,八年级 56班（音乐）,八年级 57班（音乐）,八年级 58班（音乐）,八年级 59班（音乐）,八年级 60班（音乐）,九年级 47班（音乐）,九年级 48班（音乐）,九年级 49班（音乐）</t>
-  </si>
-  <si>
-    <t>七年级 61班（语文）,七年级 62班（语文）</t>
-  </si>
-  <si>
-    <t>八年级 54班（英语）,八年级 55班（英语）</t>
-  </si>
-  <si>
-    <t>九年级 40班（音乐）,九年级 41班（音乐）,九年级 42班（音乐）,九年级 43班（音乐）,九年级 44班（音乐）,七年级 61班（音乐）,七年级 62班（音乐）,七年级 63班（音乐）,七年级 64班（音乐）,七年级 65班（音乐）,七年级 66班（音乐）,七年级 67班（音乐）,七年级 68班（音乐）,七年级 69班（音乐）,七年级 70班（音乐）,七年级 71班（音乐）,七年级 72班（音乐）</t>
-  </si>
-  <si>
-    <t>七年级 71班（英语）,七年级 72班（英语）</t>
-  </si>
-  <si>
-    <t>七年级 71班（语文）,七年级 72班（语文）</t>
-  </si>
-  <si>
-    <t>八年级 54班（物理）,八年级 55班（物理）,八年级 58班（物理）,七年级 70班（物理）,七年级 71班（物理）,七年级 72班（物理）</t>
-  </si>
-  <si>
-    <t>九年级 40班（地理）,九年级 41班（地理）,九年级 42班（地理）,九年级 43班（地理）,九年级 44班（地理）,七年级 67班（地理）,七年级 68班（地理）,七年级 69班（地理）,七年级 70班（地理）,七年级 71班（地理）,七年级 72班（地理）</t>
-  </si>
-  <si>
-    <t>九年级 43班（语文）,九年级 44班（语文）</t>
-  </si>
-  <si>
-    <t>九年级 48班（数学）,九年级 49班（数学）</t>
-  </si>
-  <si>
-    <t>九年级 46班（数学）,九年级 47班（数学）</t>
-  </si>
-  <si>
-    <t>九年级 47班（英语）,九年级 48班（英语）</t>
-  </si>
-  <si>
-    <t>七年级 61班（历史）,七年级 62班（历史）,七年级 63班（历史）,七年级 64班（历史）</t>
-  </si>
-  <si>
-    <t>九年级 44班（英语）,九年级 49班（英语）</t>
-  </si>
-  <si>
-    <t>九年级 40班（英语）,九年级 41班（英语）</t>
-  </si>
-  <si>
-    <t>八年级 53班（数学）</t>
-  </si>
-  <si>
-    <t>七年级 71班（数学）,七年级 72班（数学）</t>
-  </si>
-  <si>
-    <t>八年级 52班（语文）,八年级 53班（语文）</t>
-  </si>
-  <si>
-    <t>八年级 52班（英语）,八年级 53班（英语）</t>
-  </si>
-  <si>
-    <t>八年级 59班（英语）,八年级 60班（英语）</t>
-  </si>
-  <si>
-    <t>七年级 63班（英语）,七年级 64班（英语）</t>
-  </si>
-  <si>
-    <t>八年级 54班（语文）,八年级 55班（语文）</t>
-  </si>
-  <si>
-    <t>八年级 50班（语文）,八年级 51班（语文）</t>
-  </si>
-  <si>
-    <t>八年级 58班（语文）</t>
-  </si>
-  <si>
-    <t>八年级 56班（数学）,八年级 57班（数学）</t>
-  </si>
-  <si>
-    <t>八年级 54班（体育）,八年级 55班（体育）,八年级 56班（体育）,七年级 61班（体育）,七年级 62班（体育）,七年级 63班（体育）,七年级 64班（体育）</t>
-  </si>
-  <si>
-    <t>九年级 48班（物理）,九年级 49班（物理）,九年级 42班（物理）</t>
-  </si>
-  <si>
-    <t>九年级 42班（化学）,九年级 44班（化学）,九年级 48班（化学）</t>
-  </si>
-  <si>
-    <t>八年级 52班（地理）,八年级 59班（地理）,八年级 60班（地理）,九年级 45班（地理）,九年级 46班（地理）,八年级 53班（地理）,八年级 58班（地理）</t>
-  </si>
-  <si>
-    <t>七年级 61班（生物）,七年级 62班（生物）,七年级 67班（生物）,七年级 68班（生物）,七年级 69班（生物）,七年级 70班（生物）</t>
-  </si>
-  <si>
-    <t>八年级 60班（数学）,八年级 52班（数学）</t>
-  </si>
-  <si>
-    <t>七年级 65班（英语）,七年级 66班（英语）</t>
-  </si>
-  <si>
-    <t>七年级 67班（数学）,七年级 68班（数学）</t>
-  </si>
-  <si>
-    <t>八年级 53班（政治,道德与法治）,八年级 54班（政治,道德与法治）,八年级 55班（政治）,七年级 67班（政治）,七年级 68班（政治,道德与法治）,七年级 69班（道德与法治）,七年级 70班（道德与法治）</t>
-  </si>
-  <si>
-    <t>七年级 65班（历史）,七年级 66班（历史）,七年级 67班（历史）,七年级 68班（历史）,七年级 69班（历史）</t>
-  </si>
-  <si>
-    <t>七年级 61班（地理）,七年级 62班（地理）,七年级 63班（地理）,七年级 64班（地理）,七年级 65班（地理）,七年级 66班（地理）</t>
-  </si>
-  <si>
-    <t>七年级 67班（英语）,七年级 68班（英语）</t>
-  </si>
-  <si>
-    <t>九年级 47班（历史）,九年级 48班（历史）,九年级 49班（历史）,七年级 70班（历史）,七年级 71班（历史）,七年级 72班（历史）</t>
-  </si>
-  <si>
-    <t>七年级 69班（数学）,七年级 70班（数学）</t>
-  </si>
-  <si>
-    <t>九年级 44班（数学）,九年级 45班（数学）</t>
-  </si>
-  <si>
-    <t>七年级 63班（语文）,七年级 64班（语文）</t>
-  </si>
-  <si>
-    <t>七年级 66班（语文）,七年级 65班（语文）</t>
-  </si>
-  <si>
-    <t>八年级 50班（体育）,八年级 51班（体育）,八年级 52班（体育）,八年级 53班（体育）,七年级 68班（体育）,七年级 69班（体育）</t>
-  </si>
-  <si>
-    <t>八年级 51班（物理）,八年级 52班（物理）,八年级 50班（物理）,七年级 61班（物理）,七年级 62班（物理）,七年级 63班（物理）,七年级 64班（物理）,七年级 65班（物理）,七年级 66班（物理）</t>
-  </si>
-  <si>
-    <t>七年级 61班（数学）,七年级 62班（数学）</t>
-  </si>
-  <si>
-    <t>九年级 47班（体育）,九年级 48班（体育）,九年级 49班（体育）,七年级 70班（体育）,七年级 71班（体育）,七年级 72班（体育）</t>
-  </si>
-  <si>
     <t>七年级 61班（道德与法治）,七年级 62班（道德与法治）,七年级 63班（道德与法治）</t>
   </si>
   <si>
+    <t>李春凤</t>
+  </si>
+  <si>
+    <t>18108727416</t>
+  </si>
+  <si>
     <t>九年级 41班（语文）</t>
   </si>
   <si>
+    <t>金云燕</t>
+  </si>
+  <si>
+    <t>15198353548</t>
+  </si>
+  <si>
+    <t>赵镕</t>
+  </si>
+  <si>
+    <t>13987232866</t>
+  </si>
+  <si>
     <t>七年级 61班（英语）,七年级 62班（英语）</t>
-  </si>
-  <si>
-    <t>13988585939</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>冯云炜</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>李扬</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>15317636702</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>李春凤</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>金云燕</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>15198353548</t>
-  </si>
-  <si>
-    <t>赵镕</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>13987232866</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>索懿</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>15187209824</t>
-  </si>
-  <si>
-    <t>18487130341</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>18108727416</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>备课组长,班主任,学科组长</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>备课组长,校长</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -715,26 +808,356 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -757,31 +1180,317 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1068,878 +1777,884 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D102"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="17.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="33.6640625" customWidth="1"/>
-    <col min="4" max="4" width="48.6640625" customWidth="1"/>
+    <col min="1" max="1" width="17.8333333333333" customWidth="1"/>
+    <col min="2" max="2" width="14.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="43.625" customWidth="1"/>
+    <col min="4" max="4" width="48.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>216</v>
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>206</v>
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="3">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1">
         <v>15887863943</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1">
         <v>18487746413</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="3">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1">
         <v>18887201923</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="3">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1">
         <v>13368723303</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>115</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="3">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1">
         <v>18308720519</v>
       </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="3">
+        <v>26</v>
+      </c>
+      <c r="B9" s="1">
         <v>18289736172</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="3">
+        <v>29</v>
+      </c>
+      <c r="B10" s="1">
         <v>18087298895</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="3">
+        <v>32</v>
+      </c>
+      <c r="B11" s="1">
         <v>18869801127</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="3">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1">
         <v>18288668478</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="3">
+        <v>38</v>
+      </c>
+      <c r="B13" s="1">
         <v>15722403796</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="3">
+        <v>40</v>
+      </c>
+      <c r="B14" s="1">
         <v>18314429407</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="3">
+        <v>43</v>
+      </c>
+      <c r="B15" s="1">
         <v>13013377287</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="3">
+        <v>45</v>
+      </c>
+      <c r="B16" s="1">
         <v>15531882082</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>124</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="3">
+        <v>48</v>
+      </c>
+      <c r="B17" s="1">
         <v>15005940154</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>207</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>217</v>
+        <v>51</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="3">
+        <v>53</v>
+      </c>
+      <c r="B19" s="1">
         <v>15025103745</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="3">
+        <v>56</v>
+      </c>
+      <c r="B20" s="1">
         <v>18314551871</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>127</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="3">
+        <v>59</v>
+      </c>
+      <c r="B21" s="1">
         <v>13817946206</v>
       </c>
       <c r="D21" t="s">
-        <v>128</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="3">
+        <v>61</v>
+      </c>
+      <c r="B22" s="1">
         <v>13529010135</v>
       </c>
       <c r="D22" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="3">
+        <v>63</v>
+      </c>
+      <c r="B23" s="1">
         <v>15125008966</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>64</v>
       </c>
       <c r="D23" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="3">
+        <v>66</v>
+      </c>
+      <c r="B24" s="1">
         <v>18469751169</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
-        <v>131</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="3">
+        <v>69</v>
+      </c>
+      <c r="B25" s="1">
         <v>18987235386</v>
       </c>
       <c r="D25" t="s">
-        <v>132</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="3">
+        <v>71</v>
+      </c>
+      <c r="B26" s="1">
         <v>18787222113</v>
       </c>
       <c r="C26" t="s">
-        <v>219</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="3">
+        <v>74</v>
+      </c>
+      <c r="B27" s="1">
         <v>14787886801</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="3">
+        <v>76</v>
+      </c>
+      <c r="B28" s="1">
         <v>18487153893</v>
       </c>
       <c r="D28" t="s">
-        <v>135</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="3">
+        <v>78</v>
+      </c>
+      <c r="B29" s="1">
         <v>13211909779</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="D29" t="s">
-        <v>136</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="3">
+        <v>81</v>
+      </c>
+      <c r="B30" s="1">
         <v>18487746247</v>
       </c>
       <c r="D30" t="s">
-        <v>137</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" s="3">
+        <v>83</v>
+      </c>
+      <c r="B31" s="1">
         <v>18387134537</v>
       </c>
       <c r="C31" t="s">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>138</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" s="3">
+        <v>85</v>
+      </c>
+      <c r="B32" s="1">
         <v>15908722806</v>
       </c>
       <c r="C32" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="D32" t="s">
-        <v>139</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="3">
+        <v>88</v>
+      </c>
+      <c r="B33" s="1">
         <v>18313158390</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="D33" t="s">
-        <v>140</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" s="3">
+        <v>91</v>
+      </c>
+      <c r="B34" s="1">
         <v>18755288689</v>
       </c>
       <c r="D34" t="s">
-        <v>141</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" s="3">
+        <v>93</v>
+      </c>
+      <c r="B35" s="1">
         <v>18487358278</v>
       </c>
       <c r="D35" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36" s="3">
+        <v>95</v>
+      </c>
+      <c r="B36" s="1">
         <v>18687288766</v>
       </c>
       <c r="C36" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D36" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="3">
+        <v>98</v>
+      </c>
+      <c r="B37" s="1">
         <v>18846501021</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="3">
+        <v>99</v>
+      </c>
+      <c r="B38" s="1">
         <v>15981952327</v>
       </c>
       <c r="D38" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="3">
+        <v>101</v>
+      </c>
+      <c r="B39" s="1">
         <v>18468042276</v>
       </c>
       <c r="D39" t="s">
-        <v>145</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="3">
+        <v>103</v>
+      </c>
+      <c r="B40" s="1">
         <v>13150636145</v>
       </c>
       <c r="C40" t="s">
-        <v>105</v>
+        <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>146</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="3">
+        <v>105</v>
+      </c>
+      <c r="B41" s="1">
         <v>15752739591</v>
       </c>
       <c r="C41" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D41" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="3">
+        <v>108</v>
+      </c>
+      <c r="B42" s="1">
         <v>13759413114</v>
       </c>
       <c r="C42" t="s">
         <v>109</v>
       </c>
       <c r="D42" t="s">
-        <v>148</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="3">
+        <v>111</v>
+      </c>
+      <c r="B43" s="1">
         <v>15877710974</v>
       </c>
       <c r="C43" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D43" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44" s="3">
+        <v>114</v>
+      </c>
+      <c r="B44" s="1">
         <v>13529276921</v>
       </c>
       <c r="C44" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D44" t="s">
-        <v>150</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45" s="3">
+        <v>117</v>
+      </c>
+      <c r="B45" s="1">
         <v>15812198534</v>
       </c>
       <c r="C45" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D45" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>46</v>
-      </c>
-      <c r="B46" s="3">
+        <v>120</v>
+      </c>
+      <c r="B46" s="1">
         <v>15187202153</v>
       </c>
       <c r="C46" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="D46" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>47</v>
-      </c>
-      <c r="B47" s="3">
+        <v>123</v>
+      </c>
+      <c r="B47" s="1">
         <v>18287208090</v>
       </c>
       <c r="C47" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="D47" t="s">
-        <v>153</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>48</v>
-      </c>
-      <c r="B48" s="3">
+        <v>125</v>
+      </c>
+      <c r="B48" s="1">
         <v>17608720480</v>
       </c>
       <c r="C48" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="D48" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>49</v>
-      </c>
-      <c r="B49" s="3">
+        <v>128</v>
+      </c>
+      <c r="B49" s="1">
         <v>18288938475</v>
       </c>
       <c r="D49" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>50</v>
-      </c>
-      <c r="B50" s="3">
+        <v>130</v>
+      </c>
+      <c r="B50" s="1">
         <v>18314486446</v>
       </c>
+      <c r="C50" t="s">
+        <v>131</v>
+      </c>
       <c r="D50" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>51</v>
-      </c>
-      <c r="B51" s="3">
+        <v>133</v>
+      </c>
+      <c r="B51" s="1">
         <v>13988522021</v>
       </c>
       <c r="C51" t="s">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="D51" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>52</v>
-      </c>
-      <c r="B52" s="3">
+        <v>135</v>
+      </c>
+      <c r="B52" s="1">
         <v>18213319641</v>
       </c>
       <c r="C52" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="D52" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>53</v>
-      </c>
-      <c r="B53" s="3">
+        <v>138</v>
+      </c>
+      <c r="B53" s="1">
         <v>13187699620</v>
       </c>
       <c r="C53" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="D53" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>54</v>
-      </c>
-      <c r="B54" s="3">
+        <v>141</v>
+      </c>
+      <c r="B54" s="1">
         <v>16608801993</v>
       </c>
       <c r="C54" t="s">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="D54" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>55</v>
-      </c>
-      <c r="B55" s="3">
+        <v>143</v>
+      </c>
+      <c r="B55" s="1">
         <v>18388106054</v>
       </c>
       <c r="C55" t="s">
-        <v>105</v>
+        <v>33</v>
       </c>
       <c r="D55" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>56</v>
-      </c>
-      <c r="B56" s="3">
+        <v>145</v>
+      </c>
+      <c r="B56" s="1">
         <v>15287650795</v>
       </c>
       <c r="D56" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>208</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>209</v>
+        <v>147</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="D57" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>57</v>
-      </c>
-      <c r="B58" s="3">
+        <v>150</v>
+      </c>
+      <c r="B58" s="1">
         <v>15012192774</v>
       </c>
       <c r="C58" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="D58" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>58</v>
-      </c>
-      <c r="B59" s="3">
+        <v>153</v>
+      </c>
+      <c r="B59" s="1">
         <v>18814778377</v>
       </c>
       <c r="C59" t="s">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="D59" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>59</v>
-      </c>
-      <c r="B60" s="3">
+        <v>156</v>
+      </c>
+      <c r="B60" s="1">
         <v>18184806211</v>
       </c>
       <c r="C60" t="s">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="D60" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>60</v>
-      </c>
-      <c r="B61" s="3">
+        <v>159</v>
+      </c>
+      <c r="B61" s="1">
         <v>18313165726</v>
       </c>
       <c r="D61" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>61</v>
-      </c>
-      <c r="B62" s="3">
+        <v>161</v>
+      </c>
+      <c r="B62" s="1">
         <v>18388149392</v>
       </c>
       <c r="C62" t="s">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="D62" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>62</v>
-      </c>
-      <c r="B63" s="3">
+        <v>164</v>
+      </c>
+      <c r="B63" s="1">
         <v>13846003729</v>
       </c>
       <c r="D63" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>63</v>
-      </c>
-      <c r="B64" s="3">
+        <v>166</v>
+      </c>
+      <c r="B64" s="1">
         <v>13577243858</v>
       </c>
       <c r="C64" t="s">
-        <v>104</v>
+        <v>167</v>
       </c>
       <c r="D64" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>60</v>
-      </c>
-      <c r="B65" s="3">
+        <v>159</v>
+      </c>
+      <c r="B65" s="1">
         <v>18313165726</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>64</v>
-      </c>
-      <c r="B66" s="3">
+        <v>169</v>
+      </c>
+      <c r="B66" s="1">
         <v>18388927001</v>
       </c>
       <c r="D66" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>65</v>
-      </c>
-      <c r="B67" s="3">
+        <v>171</v>
+      </c>
+      <c r="B67" s="1">
         <v>15750023685</v>
       </c>
       <c r="D67" t="s">
@@ -1948,412 +2663,407 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>66</v>
-      </c>
-      <c r="B68" s="3">
+        <v>173</v>
+      </c>
+      <c r="B68" s="1">
         <v>18787264587</v>
       </c>
       <c r="D68" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>67</v>
-      </c>
-      <c r="B69" s="3">
+        <v>175</v>
+      </c>
+      <c r="B69" s="1">
         <v>18108723792</v>
       </c>
       <c r="C69" t="s">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="D69" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>68</v>
-      </c>
-      <c r="B70" s="3">
+        <v>178</v>
+      </c>
+      <c r="B70" s="1">
         <v>18398496995</v>
       </c>
       <c r="C70" t="s">
-        <v>101</v>
+        <v>179</v>
       </c>
       <c r="D70" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>69</v>
-      </c>
-      <c r="B71" s="3">
+        <v>181</v>
+      </c>
+      <c r="B71" s="1">
         <v>17860565076</v>
       </c>
       <c r="C71" t="s">
-        <v>101</v>
+        <v>182</v>
       </c>
       <c r="D71" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>70</v>
-      </c>
-      <c r="B72" s="3">
+        <v>184</v>
+      </c>
+      <c r="B72" s="1">
         <v>17708824508</v>
       </c>
       <c r="D72" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>71</v>
-      </c>
-      <c r="B73" s="3">
+        <v>186</v>
+      </c>
+      <c r="B73" s="1">
         <v>18287203001</v>
       </c>
+      <c r="C73" t="s">
+        <v>187</v>
+      </c>
       <c r="D73" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>72</v>
-      </c>
-      <c r="B74" s="3">
+        <v>189</v>
+      </c>
+      <c r="B74" s="1">
         <v>18287272016</v>
       </c>
       <c r="D74" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>73</v>
-      </c>
-      <c r="B75" s="3">
+        <v>191</v>
+      </c>
+      <c r="B75" s="1">
         <v>18887241242</v>
       </c>
       <c r="D75" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>74</v>
-      </c>
-      <c r="B76" s="3">
+        <v>193</v>
+      </c>
+      <c r="B76" s="1">
         <v>17869038571</v>
       </c>
       <c r="D76" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>75</v>
-      </c>
-      <c r="B77" s="3">
+        <v>195</v>
+      </c>
+      <c r="B77" s="1">
         <v>18288334595</v>
       </c>
       <c r="D77" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>76</v>
-      </c>
-      <c r="B78" s="3">
+        <v>197</v>
+      </c>
+      <c r="B78" s="1">
         <v>15025112743</v>
       </c>
       <c r="D78" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>77</v>
-      </c>
-      <c r="B79" s="3">
+        <v>199</v>
+      </c>
+      <c r="B79" s="1">
         <v>18788544986</v>
       </c>
+      <c r="C79" t="s">
+        <v>200</v>
+      </c>
       <c r="D79" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>78</v>
-      </c>
-      <c r="B80" s="3">
+        <v>202</v>
+      </c>
+      <c r="B80" s="1">
         <v>18313923241</v>
       </c>
       <c r="D80" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>79</v>
-      </c>
-      <c r="B81" s="3">
+        <v>204</v>
+      </c>
+      <c r="B81" s="1">
         <v>15087119724</v>
       </c>
       <c r="D81" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>80</v>
-      </c>
-      <c r="B82" s="3">
-        <v>15187209824</v>
-      </c>
-      <c r="C82" t="s">
-        <v>220</v>
+        <v>206</v>
+      </c>
+      <c r="B82" s="1">
+        <v>14736520796</v>
+      </c>
+      <c r="D82" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>81</v>
-      </c>
-      <c r="B83" s="3">
-        <v>14736520796</v>
+        <v>208</v>
+      </c>
+      <c r="B83" s="1">
+        <v>13978167648</v>
       </c>
       <c r="D83" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>82</v>
-      </c>
-      <c r="B84" s="3">
-        <v>13978167648</v>
+        <v>210</v>
+      </c>
+      <c r="B84" s="1">
+        <v>15911248406</v>
       </c>
       <c r="D84" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>83</v>
-      </c>
-      <c r="B85" s="3">
-        <v>15911248406</v>
+        <v>212</v>
+      </c>
+      <c r="B85" s="1">
+        <v>15752754329</v>
       </c>
       <c r="D85" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>84</v>
-      </c>
-      <c r="B86" s="3">
-        <v>15752754329</v>
+        <v>214</v>
+      </c>
+      <c r="B86" s="1">
+        <v>18191176519</v>
+      </c>
+      <c r="C86" t="s">
+        <v>33</v>
       </c>
       <c r="D86" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>85</v>
-      </c>
-      <c r="B87" s="3">
-        <v>18191176519</v>
-      </c>
-      <c r="C87" t="s">
-        <v>105</v>
+        <v>216</v>
+      </c>
+      <c r="B87" s="1">
+        <v>18288515435</v>
       </c>
       <c r="D87" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>86</v>
-      </c>
-      <c r="B88" s="3">
-        <v>18288515435</v>
+        <v>218</v>
+      </c>
+      <c r="B88" s="1">
+        <v>13619424616</v>
+      </c>
+      <c r="C88" t="s">
+        <v>219</v>
       </c>
       <c r="D88" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>87</v>
-      </c>
-      <c r="B89" s="3">
-        <v>13619424616</v>
-      </c>
-      <c r="C89" t="s">
-        <v>101</v>
+        <v>221</v>
+      </c>
+      <c r="B89" s="1">
+        <v>13320551267</v>
       </c>
       <c r="D89" t="s">
-        <v>193</v>
+        <v>222</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>88</v>
-      </c>
-      <c r="B90" s="3">
-        <v>13320551267</v>
+        <v>223</v>
+      </c>
+      <c r="B90" s="1">
+        <v>15912661481</v>
       </c>
       <c r="D90" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>89</v>
-      </c>
-      <c r="B91" s="3">
-        <v>15912661481</v>
+        <v>225</v>
+      </c>
+      <c r="B91" s="1">
+        <v>18988498823</v>
       </c>
       <c r="D91" t="s">
-        <v>195</v>
+        <v>226</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>90</v>
-      </c>
-      <c r="B92" s="3">
-        <v>18988498823</v>
+        <v>227</v>
+      </c>
+      <c r="B92" s="1">
+        <v>18487159755</v>
+      </c>
+      <c r="C92" t="s">
+        <v>228</v>
       </c>
       <c r="D92" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>91</v>
-      </c>
-      <c r="B93" s="3">
-        <v>18487159755</v>
-      </c>
-      <c r="C93" t="s">
-        <v>101</v>
+        <v>230</v>
+      </c>
+      <c r="B93" s="1">
+        <v>15368296687</v>
       </c>
       <c r="D93" t="s">
-        <v>197</v>
+        <v>231</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>92</v>
-      </c>
-      <c r="B94" s="3">
-        <v>15368296687</v>
+        <v>232</v>
+      </c>
+      <c r="B94" s="1">
+        <v>14787852549</v>
       </c>
       <c r="D94" t="s">
-        <v>198</v>
+        <v>233</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>93</v>
-      </c>
-      <c r="B95" s="3">
-        <v>14787852549</v>
+        <v>234</v>
+      </c>
+      <c r="B95" s="1">
+        <v>18469778520</v>
       </c>
       <c r="D95" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>94</v>
-      </c>
-      <c r="B96" s="3">
-        <v>18469778520</v>
+        <v>236</v>
+      </c>
+      <c r="B96" s="1">
+        <v>18869846449</v>
+      </c>
+      <c r="C96" t="s">
+        <v>237</v>
       </c>
       <c r="D96" t="s">
-        <v>200</v>
+        <v>238</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>95</v>
-      </c>
-      <c r="B97" s="3">
-        <v>18869846449</v>
-      </c>
-      <c r="C97" t="s">
-        <v>101</v>
+        <v>239</v>
+      </c>
+      <c r="B97" s="1">
+        <v>18388879229</v>
       </c>
       <c r="D97" t="s">
-        <v>201</v>
+        <v>240</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>96</v>
-      </c>
-      <c r="B98" s="3">
-        <v>18388879229</v>
+        <v>241</v>
+      </c>
+      <c r="B98" s="1">
+        <v>18213319416</v>
       </c>
       <c r="D98" t="s">
-        <v>202</v>
+        <v>242</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>97</v>
-      </c>
-      <c r="B99" s="3">
-        <v>18213319416</v>
+        <v>243</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>244</v>
       </c>
       <c r="D99" t="s">
-        <v>203</v>
+        <v>245</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>210</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>218</v>
+        <v>246</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>247</v>
       </c>
       <c r="D100" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>211</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>212</v>
+        <v>248</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>249</v>
       </c>
       <c r="D101" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
-      <c r="A102" t="s">
-        <v>213</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="D102" t="s">
-        <v>205</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>